--- a/data/raw/지도캐시.xlsx
+++ b/data/raw/지도캐시.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5013"/>
+  <dimension ref="A1:C5014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85561,6 +85561,23 @@
         </is>
       </c>
     </row>
+    <row r="5014">
+      <c r="A5014" t="inlineStr">
+        <is>
+          <t>미추홀구 주안동 130-1</t>
+        </is>
+      </c>
+      <c r="B5014" t="inlineStr">
+        <is>
+          <t>37.4643316</t>
+        </is>
+      </c>
+      <c r="C5014" t="inlineStr">
+        <is>
+          <t>126.6827674</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/raw/지도캐시.xlsx
+++ b/data/raw/지도캐시.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5014"/>
+  <dimension ref="A1:C5017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85578,6 +85578,57 @@
         </is>
       </c>
     </row>
+    <row r="5015">
+      <c r="A5015" t="inlineStr">
+        <is>
+          <t>부평구 부평동 159-10</t>
+        </is>
+      </c>
+      <c r="B5015" t="inlineStr">
+        <is>
+          <t>37.4917741</t>
+        </is>
+      </c>
+      <c r="C5015" t="inlineStr">
+        <is>
+          <t>126.7256234</t>
+        </is>
+      </c>
+    </row>
+    <row r="5016">
+      <c r="A5016" t="inlineStr">
+        <is>
+          <t>부평구 부평동 199-5</t>
+        </is>
+      </c>
+      <c r="B5016" t="inlineStr">
+        <is>
+          <t>37.4936723</t>
+        </is>
+      </c>
+      <c r="C5016" t="inlineStr">
+        <is>
+          <t>126.723537</t>
+        </is>
+      </c>
+    </row>
+    <row r="5017">
+      <c r="A5017" t="inlineStr">
+        <is>
+          <t>미추홀구 용현동 565-93</t>
+        </is>
+      </c>
+      <c r="B5017" t="inlineStr">
+        <is>
+          <t>37.4563757</t>
+        </is>
+      </c>
+      <c r="C5017" t="inlineStr">
+        <is>
+          <t>126.6390006</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
